--- a/diseases/d018/2015-2019.xlsx
+++ b/diseases/d018/2015-2019.xlsx
@@ -769,11 +769,11 @@
         <v>9</v>
       </c>
       <c r="R2" t="n">
-        <v>0.07277237526913097</v>
+        <v>0.07344967685033905</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1654,11 +1654,11 @@
         <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0.05013844752794456</v>
+        <v>0.05060509231814699</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2539,11 +2539,11 @@
         <v>7</v>
       </c>
       <c r="R14" t="n">
-        <v>0.05794572007158164</v>
+        <v>0.05848502812197273</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -3424,11 +3424,11 @@
         <v>9</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0578740937179703</v>
+        <v>0.0584127351329468</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -4309,11 +4309,11 @@
         <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>0.07241424350107421</v>
+        <v>0.07308821190520944</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -5342,11 +5342,11 @@
         <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>0.07714158283942328</v>
+        <v>0.07785954918092043</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -6227,11 +6227,11 @@
         <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>0.05443602874462553</v>
+        <v>0.05494267165970244</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -7260,11 +7260,11 @@
         <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>0.03137234288177103</v>
+        <v>0.03166432919335483</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -8145,11 +8145,11 @@
         <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>0.03201698006427317</v>
+        <v>0.03231496609458814</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -9030,11 +9030,11 @@
         <v>6</v>
       </c>
       <c r="R58" t="n">
-        <v>0.05565367675601847</v>
+        <v>0.05617165247314315</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -10063,11 +10063,11 @@
         <v>9</v>
       </c>
       <c r="R65" t="n">
-        <v>0.1156049347287179</v>
+        <v>0.1166808842878418</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10948,11 +10948,11 @@
         <v>8</v>
       </c>
       <c r="R71" t="n">
-        <v>0.09705370914337841</v>
+        <v>0.09795700013012738</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11833,11 +11833,11 @@
         <v>6</v>
       </c>
       <c r="R77" t="n">
-        <v>0.06759005883192561</v>
+        <v>0.06815961847851069</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -12866,11 +12866,11 @@
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0.04586722643599588</v>
+        <v>0.04625373477361526</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -13751,11 +13751,11 @@
         <v>5</v>
       </c>
       <c r="R90" t="n">
-        <v>0.05306068896710704</v>
+        <v>0.05350781429556423</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -14636,11 +14636,11 @@
         <v>2</v>
       </c>
       <c r="R96" t="n">
-        <v>0.04978445850739305</v>
+        <v>0.05020397609744886</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -15669,11 +15669,11 @@
         <v>4</v>
       </c>
       <c r="R103" t="n">
-        <v>0.05897214827485185</v>
+        <v>0.05946908756607677</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -16554,11 +16554,11 @@
         <v>3</v>
       </c>
       <c r="R109" t="n">
-        <v>0.06103759791249763</v>
+        <v>0.06155194208227993</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -17439,11 +17439,11 @@
         <v>2</v>
       </c>
       <c r="R115" t="n">
-        <v>0.04394422160094637</v>
+        <v>0.04431452539646058</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -18472,11 +18472,11 @@
         <v>1</v>
       </c>
       <c r="R122" t="n">
-        <v>0.02991340854521471</v>
+        <v>0.03016547920018387</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -19357,11 +19357,11 @@
         <v>2</v>
       </c>
       <c r="R128" t="n">
-        <v>0.02806162611146332</v>
+        <v>0.02829809239255343</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -20390,11 +20390,11 @@
         <v>7</v>
       </c>
       <c r="R135" t="n">
-        <v>0.04494133521912019</v>
+        <v>0.04532004136980004</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -21275,11 +21275,11 @@
         <v>8</v>
       </c>
       <c r="R141" t="n">
-        <v>0.08888555682006656</v>
+        <v>0.08963456676626062</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -22160,11 +22160,11 @@
         <v>9</v>
       </c>
       <c r="R147" t="n">
-        <v>0.08902800162266282</v>
+        <v>0.08977821190530912</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -23193,11 +23193,11 @@
         <v>3</v>
       </c>
       <c r="R154" t="n">
-        <v>0.05558093763508181</v>
+        <v>0.05606702330531172</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -24078,11 +24078,11 @@
         <v>1</v>
       </c>
       <c r="R160" t="n">
-        <v>0.04630564740553313</v>
+        <v>0.046710615594489</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -24963,11 +24963,11 @@
         <v>4</v>
       </c>
       <c r="R166" t="n">
-        <v>0.05409405904866561</v>
+        <v>0.05456714115319511</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -25996,11 +25996,11 @@
         <v>3</v>
       </c>
       <c r="R173" t="n">
-        <v>0.05253637672003911</v>
+        <v>0.05299583604145388</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -26881,11 +26881,11 @@
         <v>2</v>
       </c>
       <c r="R179" t="n">
-        <v>0.07745929397806306</v>
+        <v>0.0781367178293134</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -27766,11 +27766,11 @@
         <v>2</v>
       </c>
       <c r="R185" t="n">
-        <v>0.07823813514237631</v>
+        <v>0.07892237038518402</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -28799,11 +28799,11 @@
         <v>3</v>
       </c>
       <c r="R192" t="n">
-        <v>0.05749263867475978</v>
+        <v>0.05799544321517595</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
@@ -29684,11 +29684,11 @@
         <v>1</v>
       </c>
       <c r="R198" t="n">
-        <v>0.02895873056401078</v>
+        <v>0.02921199048646178</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
@@ -30569,11 +30569,11 @@
         <v>0</v>
       </c>
       <c r="R204" t="n">
-        <v>0.02541854345349602</v>
+        <v>0.02564084250523173</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
@@ -31602,11 +31602,11 @@
         <v>8</v>
       </c>
       <c r="R211" t="n">
-        <v>0.05409405904866561</v>
+        <v>0.05456714115319511</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
@@ -32487,11 +32487,11 @@
         <v>12</v>
       </c>
       <c r="R217" t="n">
-        <v>0.1430943630070068</v>
+        <v>0.1443458014013185</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
@@ -33372,11 +33372,11 @@
         <v>22</v>
       </c>
       <c r="R223" t="n">
-        <v>0.1490418773526716</v>
+        <v>0.1503453300097849</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
@@ -34405,11 +34405,11 @@
         <v>14</v>
       </c>
       <c r="R230" t="n">
-        <v>0.08315662808262078</v>
+        <v>0.08396126397279086</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
@@ -35290,11 +35290,11 @@
         <v>2</v>
       </c>
       <c r="R236" t="n">
-        <v>0.04214208779102308</v>
+        <v>0.04254986089468554</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
@@ -36175,11 +36175,11 @@
         <v>2</v>
       </c>
       <c r="R242" t="n">
-        <v>0.06159228215611065</v>
+        <v>0.06218825823069424</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO242" t="inlineStr">
@@ -37208,11 +37208,11 @@
         <v>5</v>
       </c>
       <c r="R249" t="n">
-        <v>0.06758237824680791</v>
+        <v>0.06823631538127664</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO249" t="inlineStr">
@@ -38093,11 +38093,11 @@
         <v>6</v>
       </c>
       <c r="R255" t="n">
-        <v>0.08830106354874902</v>
+        <v>0.0891554777609381</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO255" t="inlineStr">
@@ -38978,11 +38978,11 @@
         <v>4</v>
       </c>
       <c r="R261" t="n">
-        <v>0.07956257042820243</v>
+        <v>0.08033242968244142</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
@@ -40011,11 +40011,11 @@
         <v>5</v>
       </c>
       <c r="R268" t="n">
-        <v>0.05743445075197961</v>
+        <v>0.05799019503205471</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO268" t="inlineStr">
@@ -40896,11 +40896,11 @@
         <v>1</v>
       </c>
       <c r="R274" t="n">
-        <v>0.03608151998161173</v>
+        <v>0.03643065013056688</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO274" t="inlineStr">
@@ -41929,11 +41929,11 @@
         <v>4</v>
       </c>
       <c r="R281" t="n">
-        <v>0.02544029045578483</v>
+        <v>0.02568645448659111</v>
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO281" t="inlineStr">
@@ -42814,11 +42814,11 @@
         <v>7</v>
       </c>
       <c r="R287" t="n">
-        <v>0.06349501856139096</v>
+        <v>0.06410940579617336</v>
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO287" t="inlineStr">
@@ -43699,11 +43699,11 @@
         <v>33</v>
       </c>
       <c r="R293" t="n">
-        <v>0.155953913514271</v>
+        <v>0.157462946755751</v>
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO293" t="inlineStr">
@@ -44732,11 +44732,11 @@
         <v>17</v>
       </c>
       <c r="R300" t="n">
-        <v>0.1198019218139452</v>
+        <v>0.1209611430116478</v>
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO300" t="inlineStr">
@@ -45617,11 +45617,11 @@
         <v>8</v>
       </c>
       <c r="R306" t="n">
-        <v>0.07790545419017655</v>
+        <v>0.07864801997049813</v>
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO306" t="inlineStr">
@@ -46502,11 +46502,11 @@
         <v>3</v>
       </c>
       <c r="R312" t="n">
-        <v>0.04952510838960727</v>
+        <v>0.04999716328151594</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO312" t="inlineStr">
@@ -47387,11 +47387,11 @@
         <v>0</v>
       </c>
       <c r="R318" t="n">
-        <v>0.05184330495252507</v>
+        <v>0.0523374560308635</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO318" t="inlineStr">
@@ -48420,11 +48420,11 @@
         <v>3</v>
       </c>
       <c r="R325" t="n">
-        <v>0.04924411486682936</v>
+        <v>0.04971349143311018</v>
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO325" t="inlineStr">
@@ -49305,11 +49305,11 @@
         <v>1</v>
       </c>
       <c r="R331" t="n">
-        <v>0.06596322947211522</v>
+        <v>0.06659196641325314</v>
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO331" t="inlineStr">
@@ -50338,11 +50338,11 @@
         <v>1</v>
       </c>
       <c r="R338" t="n">
-        <v>0.07074011935933976</v>
+        <v>0.07141438783615114</v>
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO338" t="inlineStr">
@@ -51223,11 +51223,11 @@
         <v>4</v>
       </c>
       <c r="R344" t="n">
-        <v>0.04938461162821833</v>
+        <v>0.04985532735731307</v>
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO344" t="inlineStr">
@@ -52108,11 +52108,11 @@
         <v>1</v>
       </c>
       <c r="R350" t="n">
-        <v>0.02887208446543063</v>
+        <v>0.02914728242369227</v>
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO350" t="inlineStr">
@@ -53141,11 +53141,11 @@
         <v>3</v>
       </c>
       <c r="R357" t="n">
-        <v>0.02430593972028953</v>
+        <v>0.0245376148870986</v>
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO357" t="inlineStr">
@@ -54026,11 +54026,11 @@
         <v>1</v>
       </c>
       <c r="R363" t="n">
-        <v>0.04559119907071649</v>
+        <v>0.04602575740383524</v>
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO363" t="inlineStr">
@@ -54911,11 +54911,11 @@
         <v>13</v>
       </c>
       <c r="R369" t="n">
-        <v>0.1015089101035213</v>
+        <v>0.1024764552365823</v>
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO369" t="inlineStr">
@@ -55944,11 +55944,11 @@
         <v>7</v>
       </c>
       <c r="R376" t="n">
-        <v>0.09581879126726854</v>
+        <v>0.09673210030636559</v>
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO376" t="inlineStr">

--- a/diseases/d018/2015-2019.xlsx
+++ b/diseases/d018/2015-2019.xlsx
@@ -776,6 +776,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1661,6 +1671,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1806,6 +1821,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2546,6 +2566,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2691,6 +2716,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3431,6 +3461,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3576,6 +3611,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4316,6 +4356,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4609,6 +4654,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5349,6 +5399,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5494,6 +5549,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6234,6 +6294,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6379,6 +6444,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7267,6 +7337,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7412,6 +7487,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8152,6 +8232,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8297,6 +8382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9037,6 +9127,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9182,6 +9277,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10070,6 +10170,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10215,6 +10320,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10955,6 +11065,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11100,6 +11215,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11840,6 +11960,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12133,6 +12258,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12873,6 +13003,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13018,6 +13153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13758,6 +13898,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13903,6 +14048,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14643,6 +14793,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14936,6 +15091,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15676,6 +15836,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15821,6 +15986,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16561,6 +16731,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16706,6 +16881,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17446,6 +17626,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17739,6 +17924,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18479,6 +18669,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18624,6 +18819,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19364,6 +19564,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19509,6 +19714,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20397,6 +20607,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20542,6 +20757,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21282,6 +21502,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21427,6 +21652,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22167,6 +22397,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22312,6 +22547,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23200,6 +23440,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23345,6 +23590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24085,6 +24335,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24230,6 +24485,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24970,6 +25230,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25115,6 +25380,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26003,6 +26273,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26148,6 +26423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26888,6 +27168,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27033,6 +27318,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27773,6 +28063,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27918,6 +28213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28806,6 +29106,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28951,6 +29256,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29691,6 +30001,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29836,6 +30151,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30576,6 +30896,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30869,6 +31194,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31609,6 +31939,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31754,6 +32089,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32494,6 +32834,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32639,6 +32984,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33379,6 +33729,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33672,6 +34027,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34412,6 +34772,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34557,6 +34922,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35297,6 +35667,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35442,6 +35817,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36182,6 +36562,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36327,6 +36712,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37215,6 +37605,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37360,6 +37755,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38100,6 +38500,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38245,6 +38650,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38985,6 +39395,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39278,6 +39693,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40018,6 +40438,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40163,6 +40588,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40903,6 +41333,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41048,6 +41483,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41936,6 +42376,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42081,6 +42526,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42821,6 +43271,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42966,6 +43421,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43706,6 +44166,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO293" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43851,6 +44316,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44739,6 +45209,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44884,6 +45359,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45624,6 +46104,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45769,6 +46254,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46509,6 +46999,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46802,6 +47297,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47394,6 +47894,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47687,6 +48192,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48427,6 +48937,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO325" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48572,6 +49087,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49312,6 +49832,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO331" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49457,6 +49982,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO332" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50345,6 +50875,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO338" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50490,6 +51025,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO339" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51230,6 +51770,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51375,6 +51920,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52115,6 +52665,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO350" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52260,6 +52815,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO351" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53148,6 +53708,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO357" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53293,6 +53858,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO358" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54033,6 +54603,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO363" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54178,6 +54753,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO364" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54918,6 +55498,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO369" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55211,6 +55796,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO371" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55951,6 +56541,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO376" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56094,6 +56689,11 @@
       <c r="S377" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO377" t="inlineStr">
